--- a/public/templates/amazondsp-blank.xlsx
+++ b/public/templates/amazondsp-blank.xlsx
@@ -1070,7 +1070,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="621">
   <si>
     <t>Name</t>
   </si>
@@ -3780,84 +3780,6 @@
   </si>
   <si>
     <t>900x600</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -12034,7 +11956,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="20.1640625" style="83" customWidth="1"/>
@@ -12152,6 +12074,567 @@
       <c r="M3" s="124" t="s">
         <v>517</v>
       </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B4" s="112"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="57"/>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="112"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="57"/>
+      <c r="M5"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="112"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="57"/>
+      <c r="M6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="112"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="57"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B8" s="112"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="57"/>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="112"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="57"/>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="112"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="57"/>
+      <c r="M10"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="112"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="57"/>
+      <c r="M11"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="112"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="57"/>
+      <c r="M12"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="112"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="57"/>
+      <c r="M13"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="112"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="57"/>
+      <c r="M14"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B15" s="112"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="57"/>
+      <c r="M15"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B16" s="112"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="57"/>
+      <c r="M16"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B17" s="112"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="57"/>
+      <c r="M17"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B18" s="112"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="57"/>
+      <c r="M18"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B19" s="112"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="57"/>
+      <c r="M19"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B20" s="112"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="57"/>
+      <c r="M20"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B21" s="112"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="57"/>
+      <c r="M21"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B22" s="112"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="57"/>
+      <c r="M22"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B23" s="112"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="57"/>
+      <c r="M23"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B24" s="112"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="57"/>
+      <c r="M24"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B25" s="112"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="57"/>
+      <c r="M25"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B26" s="112"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="57"/>
+      <c r="M26"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B27" s="112"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="57"/>
+      <c r="M27"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="112"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="57"/>
+      <c r="M28"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B29" s="112"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="57"/>
+      <c r="M29"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B30" s="112"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="57"/>
+      <c r="M30"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B31" s="112"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="57"/>
+      <c r="M31"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B32" s="112"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="57"/>
+      <c r="M32"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B33" s="112"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="57"/>
+      <c r="M33"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B34" s="112"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="57"/>
+      <c r="M34"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B35" s="112"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="57"/>
+      <c r="M35"/>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B36" s="112"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="57"/>
+      <c r="M36"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B37" s="112"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="57"/>
+      <c r="M37"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B38" s="112"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="57"/>
+      <c r="M38"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B39" s="112"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="57"/>
+      <c r="M39"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B40" s="112"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="57"/>
+      <c r="M40"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B41" s="112"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="57"/>
+      <c r="M41"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B42" s="112"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="57"/>
+      <c r="M42"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B43" s="112"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="57"/>
+      <c r="M43"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B44" s="112"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="57"/>
+      <c r="M44"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B45" s="112"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="57"/>
+      <c r="M45"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B46" s="112"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="57"/>
+      <c r="M46"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B47" s="112"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="57"/>
+      <c r="M47"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B48" s="112"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="57"/>
+      <c r="M48"/>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B49" s="112"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="57"/>
+      <c r="M49"/>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B50" s="112"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="57"/>
+      <c r="M50"/>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B51" s="112"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="57"/>
+      <c r="M51"/>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B52" s="112"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="57"/>
+      <c r="M52"/>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B53" s="112"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="57"/>
+      <c r="M53"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B54" s="112"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="57"/>
+      <c r="M54"/>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B55" s="112"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="57"/>
+      <c r="M55"/>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B56" s="112"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="57"/>
+      <c r="M56"/>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B57" s="112"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="57"/>
+      <c r="M57"/>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B58" s="112"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="57"/>
+      <c r="M58"/>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B59" s="112"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="57"/>
+      <c r="M59"/>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B60" s="112"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="57"/>
+      <c r="M60"/>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B61" s="112"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="57"/>
+      <c r="M61"/>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B62" s="112"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="57"/>
+      <c r="M62"/>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B63" s="112"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="57"/>
+      <c r="M63"/>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B64" s="112"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="57"/>
+      <c r="M64"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B65" s="112"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="57"/>
+      <c r="M65"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B66" s="112"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="57"/>
+      <c r="M66"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B67" s="112"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="57"/>
+      <c r="M67"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B68" s="112"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="57"/>
+      <c r="M68"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B69" s="112"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="57"/>
+      <c r="M69"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B70" s="112"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="57"/>
+      <c r="M70"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B71" s="112"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="57"/>
+      <c r="M71"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B72" s="112"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="57"/>
+      <c r="M72"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B73" s="112"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="57"/>
+      <c r="M73"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B74" s="112"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="57"/>
+      <c r="M74"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B75" s="112"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="57"/>
+      <c r="M75"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B76" s="112"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="57"/>
+      <c r="M76"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B77" s="112"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="57"/>
+      <c r="M77"/>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B78" s="112"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="57"/>
+      <c r="M78"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B79" s="112"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="57"/>
+      <c r="M79"/>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B80" s="112"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="57"/>
+      <c r="M80"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B81" s="112"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="57"/>
+      <c r="M81"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B82" s="112"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="57"/>
+      <c r="M82"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B83" s="112"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="57"/>
+      <c r="M83"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B84" s="112"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="57"/>
+      <c r="M84"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B85" s="112"/>
+      <c r="J85" s="18"/>
+      <c r="K85" s="57"/>
+      <c r="M85"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B86" s="112"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="57"/>
+      <c r="M86"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B87" s="112"/>
+      <c r="J87" s="18"/>
+      <c r="K87" s="57"/>
+      <c r="M87"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B88" s="112"/>
+      <c r="J88" s="18"/>
+      <c r="K88" s="57"/>
+      <c r="M88"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B89" s="112"/>
+      <c r="J89" s="18"/>
+      <c r="K89" s="57"/>
+      <c r="M89"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B90" s="112"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="57"/>
+      <c r="M90"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B91" s="112"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="57"/>
+      <c r="M91"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B92" s="112"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="57"/>
+      <c r="M92"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B93" s="112"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="57"/>
+      <c r="M93"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B94" s="112"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="57"/>
+      <c r="M94"/>
+    </row>
+    <row r="95" spans="1:13" s="97" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="94"/>
+      <c r="B95" s="94"/>
+      <c r="C95" s="95"/>
+      <c r="D95" s="95"/>
+      <c r="E95" s="95"/>
+      <c r="F95" s="94"/>
+      <c r="G95" s="95"/>
+      <c r="H95" s="95"/>
+      <c r="I95" s="95"/>
+      <c r="J95" s="96"/>
+      <c r="K95" s="96"/>
+      <c r="L95" s="95"/>
+      <c r="M95" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="1">
